--- a/lib/app/assets/excels/default_categories_import_model.xlsx
+++ b/lib/app/assets/excels/default_categories_import_model.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Qw1exPphi6cYnG3qyV3iHuRReeBiWt6aXrQ0GsmIH3g="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OoyV3sU76jbCW3GkyNp6tJcPGpUYjwyyYKUF2EmXcZ8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>Type</t>
   </si>
@@ -348,30 +348,25 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="C4" s="1"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
@@ -379,12 +374,39 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1"/>
@@ -1375,6 +1397,9 @@
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
     <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
+    <row r="1002" ht="14.25" customHeight="1"/>
+    <row r="1003" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
